--- a/app/data/branches.xlsx
+++ b/app/data/branches.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8675"/>
+    <workbookView windowWidth="11520" windowHeight="8676"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="201">
   <si>
     <t>فروع منطقة الرياض
 مختبرات وريد الطبية للاتصال 920003694</t>
@@ -45,136 +45,205 @@
     <t>https://maps.app.goo.gl/7RKTqwjUksjCMvsN6</t>
   </si>
   <si>
+    <t>24.84928375296591, 46.66490013967251</t>
+  </si>
+  <si>
     <t>فرع قرطبة ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/48SuTJcnHjN27LMcA</t>
   </si>
   <si>
+    <t>24.807678653617028, 46.756365626983616</t>
+  </si>
+  <si>
     <t>فرع الروضة ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/FXyn23sBjoCC3boi8</t>
   </si>
   <si>
+    <t>24.737562487278627, 46.781318428836066</t>
+  </si>
+  <si>
     <t>فرع الربوة ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/HorzLnBWrWj2vz9p7</t>
   </si>
   <si>
+    <t>24.698179137281507, 46.7714686</t>
+  </si>
+  <si>
     <t>فرع لبن ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/BJiPNb2PUho7t7RA8</t>
   </si>
   <si>
+    <t>24.63214736112019, 46.565027542327876</t>
+  </si>
+  <si>
     <t>فرع العريجاء ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/odpHmhE3qvpzSLpQ6</t>
   </si>
   <si>
+    <t>24.628803183355256, 46.618339523518614</t>
+  </si>
+  <si>
     <t>فرع العليا ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/D9s3JQDa5tTQgV279</t>
   </si>
   <si>
+    <t>24.693781950059577, 46.70177482883606</t>
+  </si>
+  <si>
     <t>فرع العزيزية ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/YEFuPyUHAdZA9HVH7</t>
   </si>
   <si>
+    <t>24.574830512193028, 46.7684056693115</t>
+  </si>
+  <si>
     <t>فرع طويق ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/vstcTaxQppnckyUX7</t>
   </si>
   <si>
+    <t>24.584591168806053, 46.583118884655754</t>
+  </si>
+  <si>
     <t>فرع العارض ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/8hCRu3DBFCffiXqN8</t>
   </si>
   <si>
+    <t>24.874037568602382, 46.61641018598343</t>
+  </si>
+  <si>
     <t>فرع النسيم ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/n2UTYG5mH2dfx8BcA</t>
   </si>
   <si>
+    <t>24.747534331578738, 46.823811971163934</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Al Cheikh Hasan Ibn Hussein Ibn Ali, Riyadhفرع الحمراء ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/xF6boZ9RELk8NPKM9</t>
   </si>
   <si>
+    <t>24.782156460969635, 46.77181525581969</t>
+  </si>
+  <si>
     <t>فرع التعاون ٢٤ ساعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/NBiLwh6ktW9WA9Mq5</t>
   </si>
   <si>
+    <t>24.76532045352232, 46.693230391477535</t>
+  </si>
+  <si>
     <t>فرع السعادة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/MCYibuYz3Zytyc7X6</t>
   </si>
   <si>
+    <t>24.69772068998132, 46.84890711066564</t>
+  </si>
+  <si>
     <t>فرع الرمال</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/RwaHDGJ3YCwdXvFy7</t>
   </si>
   <si>
+    <t>24.861111726560363, 46.84272135581968</t>
+  </si>
+  <si>
     <t>فرع المهدية</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/GYJW3XvecsVLMGgJ7</t>
   </si>
   <si>
+    <t>24.660735558516595, 46.51966947301638</t>
+  </si>
+  <si>
     <t>فرع الشفا</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/JDzuwJfHcQ9y2Qzx9</t>
   </si>
   <si>
+    <t>24.537405438259945, 46.690827799999994</t>
+  </si>
+  <si>
     <t>فرع البديعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/9xA5ZB6QUy331bbs8</t>
   </si>
   <si>
+    <t>24.57326002844452, 46.663868155819685</t>
+  </si>
+  <si>
     <t>فرع النظيم</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/K5K5qLQGZNZvmg9y6</t>
   </si>
   <si>
+    <t>24.805746062161784, 46.89094659814756</t>
+  </si>
+  <si>
     <t>فرع الدار البيضاء</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/cNatQTdSQPrpTPCD7</t>
   </si>
   <si>
+    <t>24.557954910351135, 46.793984471163924</t>
+  </si>
+  <si>
     <t>فرع العقيق</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/JqqRrRgnVPndXLSd8</t>
   </si>
   <si>
+    <t>24.784687430480897, 46.626749526869766</t>
+  </si>
+  <si>
     <t>فرع الحزم</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/pbZcaL3hJxTFMbY88</t>
   </si>
   <si>
+    <t>24.548016100231827, 46.64865831163938</t>
+  </si>
+  <si>
     <t>فرع الدرعية</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/VaYd34HbTcBaZUzW9</t>
+  </si>
+  <si>
+    <t>24.747328188450897, 46.578610898147566</t>
   </si>
   <si>
     <t>فروع مختبرات وريد في جدة
@@ -187,28 +256,43 @@
     <t>https://maps.app.goo.gl/U7nFZ8h2eghVHTgq7</t>
   </si>
   <si>
+    <t>22.6368277241871, 39.07905577629778</t>
+  </si>
+  <si>
     <t>فرع الياقوت تم الإفتتاح</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/mthfUBDXahisNFCd6</t>
   </si>
   <si>
+    <t>21.775640369413864, 39.10425323558197</t>
+  </si>
+  <si>
     <t>فرع الحمدانية تم الإفتتاح</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/Wthdbi8DXys5kCWCA</t>
   </si>
   <si>
+    <t>21.75066811906418, 39.1924725120061</t>
+  </si>
+  <si>
     <t>فرع السامر تم الإفتتاح</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/Uw8SeRH36aBx7viw5</t>
   </si>
   <si>
+    <t>21.593880930722996, 39.23807303862301</t>
+  </si>
+  <si>
     <t>فرع المروة تم الإفتتاح</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/HR45VZLatwMWdSGu9</t>
+  </si>
+  <si>
+    <t>21.611925305014896, 39.209851742568176</t>
   </si>
   <si>
     <t xml:space="preserve">مختبرات وريد - مكة المكرمة
@@ -221,18 +305,27 @@
     <t>https://maps.app.goo.gl/Q8X8rDUYH8t6anXB6</t>
   </si>
   <si>
+    <t>21.350775911157044, 39.903233738623</t>
+  </si>
+  <si>
     <t>فرع الشوقية - تم الافتتاح</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/o435WNVwmXoJ9Qhz8</t>
   </si>
   <si>
+    <t>21.78117518807529, 39.96463075465137</t>
+  </si>
+  <si>
     <t>فرع الشرايع - قريبا الافتتاح</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/CFD1xY9gpY6pDPdk6</t>
   </si>
   <si>
+    <t>21.91972820498977, 39.84440891711596</t>
+  </si>
+  <si>
     <t>مختبرات وريد الطبية فرع الطائف- زورنا للمشاركة بدون شروط 💜 جـودة حـيـاتـكـــم وريــدنــا</t>
   </si>
   <si>
@@ -242,10 +335,16 @@
     <t>https://maps.app.goo.gl/DcRhXrxeFcgPwqBK9</t>
   </si>
   <si>
+    <t>21.25563615676815, 40.408686872213444</t>
+  </si>
+  <si>
     <t>فرع الطائف - شارع السحيلي</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/XqqSYF8UpnMJJiwY9</t>
+  </si>
+  <si>
+    <t>21.855706582743018, 40.41509479218676</t>
   </si>
   <si>
     <t xml:space="preserve">مـواقـع فـروع الـشـرقـيـة- زورنا للمشاركة بدون شروط للاتصال 8001221220 </t>
@@ -259,6 +358,9 @@
     <t>https://maps.app.goo.gl/1VBYFS7aX9kzFVoi8</t>
   </si>
   <si>
+    <t>26.481445122976016, 50.04653089259025</t>
+  </si>
+  <si>
     <t xml:space="preserve">مواقع فروع حائل - زورنا للمشاركة بدون شروط للاتصال 920003694 </t>
   </si>
   <si>
@@ -271,12 +373,18 @@
     <t>https://maps.app.goo.gl/DJsJpxCrmWjUXmjm7</t>
   </si>
   <si>
+    <t>27.471036927025455, 41.677427785319594</t>
+  </si>
+  <si>
     <t>موقع فرع حائل الثاني - طريق جدة تم الإفتتاح</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/a7Z87YT3zw8BJCcp7</t>
   </si>
   <si>
+    <t>27.5502665033439, 41.697071489584</t>
+  </si>
+  <si>
     <t xml:space="preserve"> للاتصال 920003694 مواقع فروع القصيم- زورنا للمشاركة بدون شروط</t>
   </si>
   <si>
@@ -286,28 +394,43 @@
     <t>https://maps.app.goo.gl/cq4C8CMqHKHPXpMQ9</t>
   </si>
   <si>
+    <t>26.404528949021238, 43.913876326983626</t>
+  </si>
+  <si>
     <t>فرع عنيزة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/bjFT5iksXKau4rfF9</t>
   </si>
   <si>
+    <t>26.07138965353931, 43.982069800000005</t>
+  </si>
+  <si>
     <t>فرع الرس</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/hkxtS885QgTX4dJo9</t>
   </si>
   <si>
+    <t>25.86318934719035, 43.51248774232787</t>
+  </si>
+  <si>
     <t>فرع البدائع</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/gooWgHEZ53kUuA8V8</t>
   </si>
   <si>
+    <t>26.00468318369602, 43.736597369836254</t>
+  </si>
+  <si>
     <t>فرع البكيرية</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/hQTyity1SUEZjsYY8</t>
+  </si>
+  <si>
+    <t>26.147388334138697, 43.6512875</t>
   </si>
   <si>
     <t xml:space="preserve">فروع وادي الدواسر والسليل- زورنا للمشاركة بدون شروط للاتصال 
@@ -320,12 +443,18 @@
     <t>https://maps.app.goo.gl/Xqs4TaBZFQJ5M6eTA</t>
   </si>
   <si>
+    <t>20.442141372354985, 44.86482172883606</t>
+  </si>
+  <si>
     <t>فرع السليل</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/oEA35McujBKwLz3L8</t>
   </si>
   <si>
+    <t>20.474100281057645, 45.57500509643421</t>
+  </si>
+  <si>
     <t>مواقع فروع شقراء - الزلفي - المجمعة للاتصال 920003694</t>
   </si>
   <si>
@@ -338,30 +467,45 @@
     <t>https://maps.app.goo.gl/zFA3AcbJTtvFwM2n8</t>
   </si>
   <si>
+    <t>25.229785128980215, 45.2621138134918</t>
+  </si>
+  <si>
     <t>فرع شقراء - طريق الملك سعود</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/TU5z6t8GwCvFqkzX8</t>
   </si>
   <si>
+    <t>25.239816209761162, 45.24586305581968</t>
+  </si>
+  <si>
     <t>فرع المجمعة</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/KEY5Hk5FoWi2V4n18</t>
   </si>
   <si>
+    <t>25.895093770983785, 45.39702958650819</t>
+  </si>
+  <si>
     <t xml:space="preserve"> King Abdullah Rd, Az Zilfi فرع الزلفي - طريق الملك عبدالله</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/Qycau3wCAVWRpnLb6</t>
   </si>
   <si>
+    <t>26.31489184055772, 44.82297681163937</t>
+  </si>
+  <si>
     <t>فرع الزلفي - شارع موسى بن نصير</t>
   </si>
   <si>
     <t>https://share.google/wV25WoYS4wMFFr020</t>
   </si>
   <si>
+    <t>26.395547281522862, 44.79506538448506</t>
+  </si>
+  <si>
     <t xml:space="preserve"> للاتصال 920003694  موقع فرع حفر الباطن - زورنا للمشاركة بدون شروط</t>
   </si>
   <si>
@@ -371,6 +515,9 @@
     <t>https://maps.app.goo.gl/QKNwn8YVHMwmg5UC8</t>
   </si>
   <si>
+    <t>28.418447647446207, 45.9781944</t>
+  </si>
+  <si>
     <t xml:space="preserve">مواقع فروع الدوادمي - ساجر - عفيف للاتصال 920003694 </t>
   </si>
   <si>
@@ -380,18 +527,27 @@
     <t>https://maps.app.goo.gl/dUFRrz8f2eeXCiNn6</t>
   </si>
   <si>
+    <t>24.54522496770698, 44.4441363</t>
+  </si>
+  <si>
     <t>فرع عفيف</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/nzvyZHUNDoNaHets9</t>
   </si>
   <si>
+    <t>23.900700885540296, 42.91119642698362</t>
+  </si>
+  <si>
     <t>فرع ساجر</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/6D48sqHtkLi4mp1h9</t>
   </si>
   <si>
+    <t>25.188008056667915, 44.601117442327876</t>
+  </si>
+  <si>
     <t>مواقع فروع الخرج - الدلم - حوطة بني تميم للاتصال 920003694</t>
   </si>
   <si>
@@ -401,30 +557,45 @@
     <t>https://maps.app.goo.gl/k8JNhKATqsngmRe78</t>
   </si>
   <si>
+    <t>24.146869402169703, 47.359427026983624</t>
+  </si>
+  <si>
     <t>فرع الدلم</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/AEHcEgix4ELgXT1z6</t>
   </si>
   <si>
+    <t>23.99607237339489, 47.13716357301637</t>
+  </si>
+  <si>
     <t>فرع حوطة بني تميم</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/MCQEpB8CgUMaH31m8</t>
   </si>
   <si>
+    <t>23.49159268165047, 46.8817044</t>
+  </si>
+  <si>
     <t>فرع الخرج</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/Q93ty5DM8EhVQWoh7</t>
   </si>
   <si>
+    <t>24.152832139724122, 47.277395</t>
+  </si>
+  <si>
     <t>فرع الافلاج</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/YJPri1Ur1izBdWMw7</t>
   </si>
   <si>
+    <t>22.29284634241132, 46.722958299999995</t>
+  </si>
+  <si>
     <t>مواقع فروع المزاحمية - القويعية للاتصال 920003694</t>
   </si>
   <si>
@@ -434,12 +605,18 @@
     <t>https://maps.app.goo.gl/yWpx66ajkeM4St6r8</t>
   </si>
   <si>
+    <t>24.05147274461968, 45.26327385581969</t>
+  </si>
+  <si>
     <t>فرع المزاحمية</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/KkEw24dLoDJWejew5</t>
   </si>
   <si>
+    <t>24.472193139828736, 46.272367842327874</t>
+  </si>
+  <si>
     <t>مواقع فروع رماح - ثادق</t>
   </si>
   <si>
@@ -449,10 +626,16 @@
     <t>https://maps.app.goo.gl/jUTwzGVzr5BoDPoPA</t>
   </si>
   <si>
+    <t>25.28459660592738, 45.86172624662706</t>
+  </si>
+  <si>
     <t>فرع رماح</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/ExRx5qL1a7KvajjD6</t>
+  </si>
+  <si>
+    <t>25.564320794373195, 47.15900177790985</t>
   </si>
 </sst>
 </file>
@@ -487,6 +670,7 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -494,7 +678,6 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -989,7 +1172,7 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1119,7 +1302,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1129,9 +1312,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1141,28 +1321,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1177,17 +1354,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1202,7 +1379,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1493,7 +1670,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="13301980"/>
+          <a:off x="0" y="13858240"/>
           <a:ext cx="243840" cy="243840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1773,785 +1950,1248 @@
   <cols>
     <col min="1" max="1" width="47.3333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="42.5555555555556" style="1" customWidth="1"/>
+    <col min="4" max="4" width="47.3333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="58" customHeight="1" spans="1:4">
+    <row r="1" ht="58" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-    </row>
-    <row r="2" ht="15" spans="1:2">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" ht="15" spans="1:2">
-      <c r="A3" s="5" t="s">
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:5">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" ht="15" spans="1:2">
-      <c r="A4" s="5" t="s">
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="4" ht="15" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" ht="15" spans="1:2">
-      <c r="A5" s="5" t="s">
-        <v>7</v>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" ht="15" spans="1:2">
-      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="B6" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" ht="15" spans="1:2">
-      <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" ht="15" spans="1:5">
+      <c r="A7" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="1:2">
-      <c r="A8" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:5">
+      <c r="A8" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" ht="15" spans="1:2">
-      <c r="A9" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:5">
+      <c r="A9" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="1:2">
-      <c r="A10" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:5">
+      <c r="A10" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" ht="15" spans="1:2">
-      <c r="A11" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:5">
+      <c r="A11" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="1:2">
-      <c r="A12" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:5">
+      <c r="A12" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" ht="15" spans="1:2">
-      <c r="A13" s="5" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:5">
+      <c r="A13" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="1:2">
-      <c r="A14" s="5" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" ht="15" spans="1:2">
-      <c r="A15" s="5" t="s">
-        <v>27</v>
+        <v>37</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="1:2">
-      <c r="A16" s="5" t="s">
-        <v>29</v>
+        <v>40</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" ht="15" spans="1:2">
-      <c r="A17" s="5" t="s">
-        <v>31</v>
+        <v>43</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="1:2">
-      <c r="A18" s="5" t="s">
-        <v>33</v>
+        <v>46</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" ht="15" spans="1:2">
-      <c r="A19" s="5" t="s">
-        <v>35</v>
+        <v>49</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:5">
+      <c r="A19" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="1:2">
-      <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:5">
+      <c r="A20" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" ht="15" spans="1:2">
-      <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>55</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:5">
+      <c r="A21" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="1:2">
-      <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>58</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:5">
+      <c r="A22" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" ht="15" spans="1:2">
-      <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>61</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:5">
+      <c r="A23" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="1:2">
-      <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>64</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:5">
+      <c r="A24" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" ht="15" spans="1:2">
-      <c r="A25" s="5" t="s">
-        <v>47</v>
+        <v>67</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:5">
+      <c r="A25" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>70</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" ht="28.8" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="B27" s="8"/>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="D27" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
-    </row>
-    <row r="29" spans="1:2">
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="8"/>
       <c r="B29" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" ht="15" spans="1:2">
-      <c r="A30" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="1:2">
-      <c r="A31" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="1:2">
-      <c r="A32" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" ht="15" spans="1:2">
-      <c r="A33" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" ht="15" spans="1:2">
-      <c r="A34" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="3" t="s">
-        <v>60</v>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" ht="15" spans="1:5">
+      <c r="A30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="1:5">
+      <c r="A31" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="1:5">
+      <c r="A32" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" ht="15" spans="1:5">
+      <c r="A33" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" ht="15" spans="1:5">
+      <c r="A34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" ht="28.8" spans="1:5">
+      <c r="A36" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="B36" s="8"/>
-    </row>
-    <row r="37" spans="1:2">
+      <c r="D36" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
-    </row>
-    <row r="38" spans="1:2">
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="8"/>
       <c r="B38" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" ht="15" spans="1:2">
-      <c r="A39" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" ht="15" spans="1:2">
-      <c r="A40" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" ht="15" spans="1:2">
-      <c r="A41" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B43" s="3"/>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3" t="s">
+      <c r="D38" s="8"/>
+    </row>
+    <row r="39" ht="15" spans="1:5">
+      <c r="A39" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" ht="15" spans="1:5">
+      <c r="A40" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E40" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" ht="15" spans="1:5">
+      <c r="A41" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" ht="28.8" spans="1:5">
+      <c r="A43" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="D43" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" ht="15" spans="1:2">
-      <c r="A45" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="46" ht="15" spans="1:2">
-      <c r="A46" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" ht="15" spans="1:5">
+      <c r="A45" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E45" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="1:5">
+      <c r="A46" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E46" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" s="8" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="B48" s="8"/>
-    </row>
-    <row r="49" spans="1:2">
+      <c r="D48" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
-    </row>
-    <row r="50" spans="1:2">
+      <c r="D49" s="8"/>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" s="8"/>
       <c r="B50" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" ht="43.2" spans="1:2">
-      <c r="A51" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="55" ht="30" spans="1:2">
+      <c r="D50" s="8"/>
+    </row>
+    <row r="51" ht="43.2" spans="1:5">
+      <c r="A51" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" s="8" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="B55" s="8"/>
-    </row>
-    <row r="56" spans="1:2">
+      <c r="D55" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
-    </row>
-    <row r="57" spans="1:2">
+      <c r="D56" s="8"/>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" s="8" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" ht="15" spans="1:2">
-      <c r="A58" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="59" ht="15" spans="1:2">
-      <c r="A59" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B61" s="11"/>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-    </row>
-    <row r="63" ht="15" spans="1:2">
-      <c r="A63" s="12" t="s">
-        <v>76</v>
+      <c r="D57" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" ht="15" spans="1:5">
+      <c r="A58" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" ht="15" spans="1:5">
+      <c r="A59" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E59" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" ht="30" spans="1:5">
+      <c r="A61" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B61" s="10"/>
+      <c r="D61" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" ht="15" spans="1:5">
+      <c r="A62" s="10"/>
+      <c r="B62" s="10"/>
+      <c r="D62" s="10"/>
+    </row>
+    <row r="63" ht="15" spans="1:5">
+      <c r="A63" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" ht="15" spans="1:2">
-      <c r="A64" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65" ht="15" spans="1:2">
-      <c r="A65" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B65" s="14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="66" ht="15" spans="1:2">
-      <c r="A66" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B66" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="67" ht="15" spans="1:2">
-      <c r="A67" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B67" s="14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="68" ht="15" spans="1:2">
-      <c r="A68" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B72" s="16"/>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="16"/>
-      <c r="B73" s="16"/>
-    </row>
-    <row r="74" ht="15" spans="1:2">
-      <c r="A74" s="12" t="s">
-        <v>76</v>
+      <c r="D63" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64" ht="15" spans="1:5">
+      <c r="A64" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E64" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" ht="15" spans="1:5">
+      <c r="A65" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E65" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" ht="15" spans="1:5">
+      <c r="A66" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="67" ht="15" spans="1:5">
+      <c r="A67" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E67" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" ht="15" spans="1:5">
+      <c r="A68" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E68" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" ht="28.8" spans="1:5">
+      <c r="A72" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B72" s="14"/>
+      <c r="D72" s="13" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="14"/>
+      <c r="B73" s="14"/>
+      <c r="D73" s="14"/>
+    </row>
+    <row r="74" ht="15" spans="1:5">
+      <c r="A74" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" ht="15" spans="1:2">
-      <c r="A75" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B75" s="14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="76" ht="15" spans="1:2">
-      <c r="A76" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B77" s="16"/>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="16"/>
-      <c r="B78" s="16"/>
-    </row>
-    <row r="79" ht="15" spans="1:2">
-      <c r="A79" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B79" s="16" t="s">
+      <c r="D74" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" ht="15" spans="1:5">
+      <c r="A75" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E75" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="76" ht="15" spans="1:5">
+      <c r="A76" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E76" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B77" s="14"/>
+      <c r="D77" s="14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="14"/>
+      <c r="B78" s="14"/>
+      <c r="D78" s="14"/>
+    </row>
+    <row r="79" ht="15" spans="1:5">
+      <c r="A79" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B79" s="14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" ht="15" spans="1:2">
-      <c r="A80" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B80" s="19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="81" ht="15" spans="1:2">
-      <c r="A81" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="82" ht="15" spans="1:2">
-      <c r="A82" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="B82" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="83" ht="30" spans="1:2">
-      <c r="A83" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="84" ht="15" spans="1:2">
-      <c r="A84" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B84" s="14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="85" ht="15" spans="1:2">
-      <c r="A85" s="18"/>
-      <c r="B85" s="14"/>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B86" s="20"/>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="20"/>
-      <c r="B87" s="20"/>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="20"/>
-      <c r="B88" s="20"/>
+      <c r="D79" s="10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="80" ht="15" spans="1:5">
+      <c r="A80" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E80" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="81" ht="15" spans="1:7">
+      <c r="A81" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E81" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="82" ht="15" spans="1:7">
+      <c r="A82" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="E82" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83" ht="30" spans="1:7">
+      <c r="A83" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E83" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="84" ht="15" spans="1:7">
+      <c r="A84" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E84" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="85" ht="15" spans="1:7">
+      <c r="A85" s="16"/>
+      <c r="B85" s="12"/>
+      <c r="D85" s="16"/>
+    </row>
+    <row r="86" ht="30" spans="1:7">
+      <c r="A86" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B86" s="10"/>
+      <c r="D86" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="87" ht="15" spans="1:7">
+      <c r="A87" s="10"/>
+      <c r="B87" s="10"/>
+      <c r="D87" s="10"/>
+    </row>
+    <row r="88" ht="15" spans="1:7">
+      <c r="A88" s="10"/>
+      <c r="B88" s="10"/>
+      <c r="D88" s="10"/>
     </row>
     <row r="89" ht="15" spans="1:7">
-      <c r="A89" s="12" t="s">
-        <v>76</v>
+      <c r="A89" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G89" s="12"/>
+      <c r="D89" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="G89" s="10"/>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E90" t="s">
+        <v>160</v>
+      </c>
+      <c r="G90" s="1"/>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="19"/>
+      <c r="B91" s="19"/>
+      <c r="D91" s="19"/>
+      <c r="G91" s="1"/>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="19"/>
+      <c r="B92" s="19"/>
+      <c r="D92" s="19"/>
+      <c r="G92" s="1"/>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="19"/>
+      <c r="B93" s="19"/>
+      <c r="D93" s="19"/>
+      <c r="G93" s="1"/>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="19"/>
+      <c r="B94" s="19"/>
+      <c r="D94" s="19"/>
+      <c r="G94" s="1"/>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B95" s="14"/>
+      <c r="D95" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G95" s="1"/>
+    </row>
+    <row r="96" ht="15" spans="1:7">
+      <c r="A96" s="14"/>
+      <c r="B96" s="14"/>
+      <c r="D96" s="14"/>
+      <c r="G96" s="10"/>
+    </row>
+    <row r="97" ht="15" spans="1:7">
+      <c r="A97" s="10" t="s">
         <v>110</v>
-      </c>
-      <c r="B90" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="G90" s="1"/>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" s="22"/>
-      <c r="B91" s="22"/>
-      <c r="G91" s="1"/>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" s="22"/>
-      <c r="B92" s="22"/>
-      <c r="G92" s="1"/>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" s="22"/>
-      <c r="B93" s="22"/>
-      <c r="G93" s="1"/>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" s="22"/>
-      <c r="B94" s="22"/>
-      <c r="G94" s="1"/>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B95" s="16"/>
-      <c r="G95" s="1"/>
-    </row>
-    <row r="96" ht="15" spans="1:7">
-      <c r="A96" s="16"/>
-      <c r="B96" s="16"/>
-      <c r="G96" s="12"/>
-    </row>
-    <row r="97" ht="15" spans="1:7">
-      <c r="A97" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G97" s="12"/>
+      <c r="D97" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="G97" s="10"/>
     </row>
     <row r="98" ht="15" spans="1:7">
-      <c r="A98" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B98" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="G98" s="12"/>
+      <c r="A98" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B98" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="E98" t="s">
+        <v>164</v>
+      </c>
+      <c r="F98"/>
+      <c r="G98" s="10"/>
     </row>
     <row r="99" ht="15" spans="1:7">
-      <c r="A99" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B99" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G99" s="12"/>
+      <c r="A99" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B99" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E99" t="s">
+        <v>167</v>
+      </c>
+      <c r="G99" s="10"/>
     </row>
     <row r="100" ht="15" spans="1:7">
-      <c r="A100" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B100" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="G100" s="12"/>
-    </row>
-    <row r="101" ht="15" spans="7:7">
+      <c r="A100" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B100" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E100" t="s">
+        <v>170</v>
+      </c>
+      <c r="G100" s="10"/>
+    </row>
+    <row r="101" spans="1:7">
       <c r="G101" s="1"/>
     </row>
     <row r="102" ht="15" spans="1:7">
-      <c r="A102" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="B102" s="16"/>
-      <c r="G102" s="12"/>
+      <c r="A102" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B102" s="14"/>
+      <c r="D102" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="G102" s="10"/>
     </row>
     <row r="103" spans="1:7">
-      <c r="A103" s="16"/>
-      <c r="B103" s="16"/>
+      <c r="A103" s="14"/>
+      <c r="B103" s="14"/>
+      <c r="D103" s="14"/>
       <c r="G103" s="1"/>
     </row>
     <row r="104" ht="15" spans="1:7">
-      <c r="A104" s="12" t="s">
-        <v>76</v>
+      <c r="A104" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G104" s="12"/>
+      <c r="D104" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="G104" s="10"/>
     </row>
     <row r="105" ht="15" spans="1:7">
-      <c r="A105" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B105" s="19" t="s">
-        <v>121</v>
+      <c r="A105" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B105" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E105" t="s">
+        <v>174</v>
       </c>
       <c r="G105" s="1"/>
     </row>
     <row r="106" ht="15" spans="1:7">
-      <c r="A106" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B106" s="19" t="s">
-        <v>123</v>
+      <c r="A106" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E106" t="s">
+        <v>177</v>
       </c>
       <c r="G106" s="1"/>
     </row>
     <row r="107" ht="15" spans="1:7">
-      <c r="A107" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B107" s="19" t="s">
-        <v>125</v>
+      <c r="A107" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B107" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E107" t="s">
+        <v>180</v>
       </c>
       <c r="G107" s="1"/>
     </row>
     <row r="108" ht="15" spans="1:7">
-      <c r="A108" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B108" s="19" t="s">
-        <v>127</v>
+      <c r="A108" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B108" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E108" t="s">
+        <v>183</v>
       </c>
       <c r="G108" s="1"/>
     </row>
     <row r="109" ht="15" spans="1:7">
-      <c r="A109" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B109" s="19" t="s">
-        <v>129</v>
+      <c r="A109" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B109" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E109" t="s">
+        <v>186</v>
       </c>
       <c r="G109" s="1"/>
     </row>
     <row r="110" spans="1:7">
-      <c r="A110" s="16"/>
-      <c r="B110" s="16"/>
+      <c r="A110" s="14"/>
+      <c r="B110" s="14"/>
+      <c r="D110" s="14"/>
       <c r="G110" s="1"/>
     </row>
     <row r="111" spans="1:7">
-      <c r="A111" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="B111" s="16"/>
+      <c r="A111" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B111" s="14"/>
+      <c r="D111" s="14" t="s">
+        <v>187</v>
+      </c>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="16"/>
-      <c r="B112" s="16"/>
-    </row>
-    <row r="113" ht="15" spans="1:2">
-      <c r="A113" s="12" t="s">
-        <v>76</v>
+    <row r="112" spans="1:7">
+      <c r="A112" s="14"/>
+      <c r="B112" s="14"/>
+      <c r="D112" s="14"/>
+    </row>
+    <row r="113" ht="15" spans="1:5">
+      <c r="A113" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" ht="15" spans="1:2">
-      <c r="A114" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="B114" s="14" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="115" ht="15" spans="1:2">
-      <c r="A115" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B116" s="16"/>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="16"/>
-      <c r="B117" s="16"/>
-    </row>
-    <row r="118" ht="15" spans="1:2">
-      <c r="A118" s="12" t="s">
-        <v>76</v>
+      <c r="D113" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="114" ht="15" spans="1:5">
+      <c r="A114" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D114" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="E114" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="115" ht="15" spans="1:5">
+      <c r="A115" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D115" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="E115" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="B116" s="14"/>
+      <c r="D116" s="14" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="14"/>
+      <c r="B117" s="14"/>
+      <c r="D117" s="14"/>
+    </row>
+    <row r="118" ht="15" spans="1:5">
+      <c r="A118" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="119" ht="15" spans="1:2">
-      <c r="A119" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="120" ht="15" spans="1:2">
-      <c r="A120" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>139</v>
+      <c r="D118" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="119" ht="15" spans="1:5">
+      <c r="A119" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="E119" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="120" ht="15" spans="1:5">
+      <c r="A120" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="E120" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2594,64 +3234,64 @@
     <hyperlink ref="A23" r:id="rId21" display="فرع العقيق" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%B9%D9%82%D9%8A%D9%82%E2%80%AD/@24.7815704,46.5735345,13.45z/data=!4m7!3m6!1s0x3e2"/>
     <hyperlink ref="A24" r:id="rId22" display="فرع الحزم" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D8%A7%D9%84%D8%AD%D8%B2%D9%85%E2%80%AD/@24.5478014,46.6509543,17z/data=!3m1!4b1!4m6!3m5!1s0x3e2f11ef6ea2d3b7:0xe875"/>
     <hyperlink ref="A25" r:id="rId23" display="فرع الدرعية" tooltip="https://maps.app.goo.gl/4P2Q5mfUQae3jFfH6"/>
-    <hyperlink ref="B4" r:id="rId24" display="https://maps.app.goo.gl/48SuTJcnHjN27LMcA"/>
-    <hyperlink ref="B8" r:id="rId25" display="https://maps.app.goo.gl/odpHmhE3qvpzSLpQ6"/>
-    <hyperlink ref="B11" r:id="rId26" display="https://maps.app.goo.gl/vstcTaxQppnckyUX7"/>
-    <hyperlink ref="B12" r:id="rId27" display="https://maps.app.goo.gl/8hCRu3DBFCffiXqN8"/>
-    <hyperlink ref="B18" r:id="rId28" display="https://maps.app.goo.gl/GYJW3XvecsVLMGgJ7"/>
-    <hyperlink ref="B20" r:id="rId29" display="https://maps.app.goo.gl/9xA5ZB6QUy331bbs8"/>
+    <hyperlink ref="B4" r:id="rId24" display="https://maps.app.goo.gl/48SuTJcnHjN27LMcA" tooltip="https://maps.app.goo.gl/48SuTJcnHjN27LMcA"/>
+    <hyperlink ref="B8" r:id="rId25" display="https://maps.app.goo.gl/odpHmhE3qvpzSLpQ6" tooltip="https://maps.app.goo.gl/odpHmhE3qvpzSLpQ6"/>
+    <hyperlink ref="B11" r:id="rId26" display="https://maps.app.goo.gl/vstcTaxQppnckyUX7" tooltip="https://maps.app.goo.gl/vstcTaxQppnckyUX7"/>
+    <hyperlink ref="B12" r:id="rId27" display="https://maps.app.goo.gl/8hCRu3DBFCffiXqN8" tooltip="https://maps.app.goo.gl/8hCRu3DBFCffiXqN8"/>
+    <hyperlink ref="B18" r:id="rId28" display="https://maps.app.goo.gl/GYJW3XvecsVLMGgJ7" tooltip="https://maps.app.goo.gl/GYJW3XvecsVLMGgJ7"/>
+    <hyperlink ref="B20" r:id="rId29" display="https://maps.app.goo.gl/9xA5ZB6QUy331bbs8" tooltip="https://maps.app.goo.gl/9xA5ZB6QUy331bbs8"/>
     <hyperlink ref="B21" r:id="rId30" display="https://maps.app.goo.gl/K5K5qLQGZNZvmg9y6" tooltip="https://maps.app.goo.gl/K5K5qLQGZNZvmg9y6"/>
-    <hyperlink ref="B23" r:id="rId31" display="https://maps.app.goo.gl/JqqRrRgnVPndXLSd8"/>
-    <hyperlink ref="B24" r:id="rId32" display="https://maps.app.goo.gl/pbZcaL3hJxTFMbY88"/>
-    <hyperlink ref="B25" r:id="rId33" display="https://maps.app.goo.gl/VaYd34HbTcBaZUzW9"/>
+    <hyperlink ref="B23" r:id="rId31" display="https://maps.app.goo.gl/JqqRrRgnVPndXLSd8" tooltip="https://maps.app.goo.gl/JqqRrRgnVPndXLSd8"/>
+    <hyperlink ref="B24" r:id="rId32" display="https://maps.app.goo.gl/pbZcaL3hJxTFMbY88" tooltip="https://maps.app.goo.gl/pbZcaL3hJxTFMbY88"/>
+    <hyperlink ref="B25" r:id="rId33" display="https://maps.app.goo.gl/VaYd34HbTcBaZUzW9" tooltip="https://maps.app.goo.gl/VaYd34HbTcBaZUzW9"/>
     <hyperlink ref="A30" r:id="rId34" display="فرع المحمدية تم الإفتتاح ٢٤ ساعة" tooltip="https://maps.app.goo.gl/c3hoJMdEFZuwm6HX7"/>
     <hyperlink ref="A31" r:id="rId35" display="فرع الياقوت تم الإفتتاح" tooltip="https://maps.app.goo.gl/6EeBJpXvKMjKZZTf6"/>
     <hyperlink ref="A32" r:id="rId36" display="فرع الحمدانية تم الإفتتاح" tooltip="https://maps.app.goo.gl/JPV4axnHsgxLXH4v6"/>
     <hyperlink ref="A33" r:id="rId37" display="فرع السامر تم الإفتتاح" tooltip="https://maps.app.goo.gl/UyVnmvGkKLbKmGJz8"/>
     <hyperlink ref="A34" r:id="rId38" display="فرع المروة تم الإفتتاح" tooltip="https://maps.app.goo.gl/DaCkbNzHF8yt2CrC9"/>
-    <hyperlink ref="B30" r:id="rId39" display="https://maps.app.goo.gl/U7nFZ8h2eghVHTgq7"/>
-    <hyperlink ref="B31" r:id="rId40" display="https://maps.app.goo.gl/mthfUBDXahisNFCd6"/>
-    <hyperlink ref="B32" r:id="rId41" display="https://maps.app.goo.gl/Wthdbi8DXys5kCWCA"/>
-    <hyperlink ref="B33" r:id="rId42" display="https://maps.app.goo.gl/Uw8SeRH36aBx7viw5"/>
-    <hyperlink ref="B34" r:id="rId43" display="https://maps.app.goo.gl/HR45VZLatwMWdSGu9"/>
+    <hyperlink ref="B30" r:id="rId39" display="https://maps.app.goo.gl/U7nFZ8h2eghVHTgq7" tooltip="https://maps.app.goo.gl/U7nFZ8h2eghVHTgq7"/>
+    <hyperlink ref="B31" r:id="rId40" display="https://maps.app.goo.gl/mthfUBDXahisNFCd6" tooltip="https://maps.app.goo.gl/mthfUBDXahisNFCd6"/>
+    <hyperlink ref="B32" r:id="rId41" display="https://maps.app.goo.gl/Wthdbi8DXys5kCWCA" tooltip="https://maps.app.goo.gl/Wthdbi8DXys5kCWCA"/>
+    <hyperlink ref="B33" r:id="rId42" display="https://maps.app.goo.gl/Uw8SeRH36aBx7viw5" tooltip="https://maps.app.goo.gl/Uw8SeRH36aBx7viw5"/>
+    <hyperlink ref="B34" r:id="rId43" display="https://maps.app.goo.gl/HR45VZLatwMWdSGu9" tooltip="https://maps.app.goo.gl/HR45VZLatwMWdSGu9"/>
     <hyperlink ref="A39" r:id="rId44" display="فرع العوالي - تم الافتتاح" tooltip="https://maps.app.goo.gl/Ab86Zf14wbbEeQjp6"/>
     <hyperlink ref="A40" r:id="rId45" display="فرع الشوقية - تم الافتتاح" tooltip="https://maps.app.goo.gl/2ndi9JxFBkWbaZqU7"/>
     <hyperlink ref="A41" r:id="rId46" display="فرع الشرايع - قريبا الافتتاح" tooltip="https://maps.app.goo.gl/GykJXxYSLrA9xqh89"/>
     <hyperlink ref="B39" r:id="rId47" display="https://maps.app.goo.gl/Q8X8rDUYH8t6anXB6" tooltip="https://maps.app.goo.gl/Q8X8rDUYH8t6anXB6"/>
-    <hyperlink ref="B40" r:id="rId48" display="https://maps.app.goo.gl/o435WNVwmXoJ9Qhz8"/>
+    <hyperlink ref="B40" r:id="rId48" display="https://maps.app.goo.gl/o435WNVwmXoJ9Qhz8" tooltip="https://maps.app.goo.gl/o435WNVwmXoJ9Qhz8"/>
     <hyperlink ref="B41" r:id="rId49" display="https://maps.app.goo.gl/CFD1xY9gpY6pDPdk6" tooltip="https://maps.app.goo.gl/CFD1xY9gpY6pDPdk6"/>
     <hyperlink ref="A45" r:id="rId50" display="فرع الطائف شارع شهار" tooltip="https://maps.app.goo.gl/tnQpq8q3UA7PWLRQ9"/>
     <hyperlink ref="A46" r:id="rId51" display="فرع الطائف - شارع السحيلي" tooltip="https://maps.app.goo.gl/N8gmy9MrJfFdrfoFA"/>
-    <hyperlink ref="B45" r:id="rId52" display="https://maps.app.goo.gl/DcRhXrxeFcgPwqBK9"/>
-    <hyperlink ref="B46" r:id="rId53" display="https://maps.app.goo.gl/XqqSYF8UpnMJJiwY9"/>
-    <hyperlink ref="B51" r:id="rId54" display="https://maps.app.goo.gl/1VBYFS7aX9kzFVoi8"/>
+    <hyperlink ref="B45" r:id="rId52" display="https://maps.app.goo.gl/DcRhXrxeFcgPwqBK9" tooltip="https://maps.app.goo.gl/DcRhXrxeFcgPwqBK9"/>
+    <hyperlink ref="B46" r:id="rId53" display="https://maps.app.goo.gl/XqqSYF8UpnMJJiwY9" tooltip="https://maps.app.goo.gl/XqqSYF8UpnMJJiwY9"/>
+    <hyperlink ref="B51" r:id="rId54" display="https://maps.app.goo.gl/1VBYFS7aX9kzFVoi8" tooltip="https://maps.app.goo.gl/1VBYFS7aX9kzFVoi8"/>
     <hyperlink ref="A58" r:id="rId55" display="موقع فرع حائل - طريق الملك سعود" tooltip="https://maps.app.goo.gl/xkZkMr7NSddrjaJW6"/>
     <hyperlink ref="A59" r:id="rId56" display="موقع فرع حائل الثاني - طريق جدة تم الإفتتاح" tooltip="https://maps.app.goo.gl/T51u2WDJKX2BviDr5"/>
-    <hyperlink ref="B58" r:id="rId57" display="https://maps.app.goo.gl/DJsJpxCrmWjUXmjm7"/>
-    <hyperlink ref="B59" r:id="rId58" display="https://maps.app.goo.gl/a7Z87YT3zw8BJCcp7"/>
+    <hyperlink ref="B58" r:id="rId57" display="https://maps.app.goo.gl/DJsJpxCrmWjUXmjm7" tooltip="https://maps.app.goo.gl/DJsJpxCrmWjUXmjm7"/>
+    <hyperlink ref="B59" r:id="rId58" display="https://maps.app.goo.gl/a7Z87YT3zw8BJCcp7" tooltip="https://maps.app.goo.gl/a7Z87YT3zw8BJCcp7"/>
     <hyperlink ref="A64" r:id="rId59" display="فرع بريدة ٢٤ ساعة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A8%D8%B1%D9%8A%D8%AF%D9%87%E2%80%AD/@26.4042432,43.9140287,1261m/data=!3m2!1e3!4b1!4m6!3m5!1s"/>
     <hyperlink ref="A65" r:id="rId60" display="فرع عنيزة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%B9%D9%86%D9%8A%D8%B2%D8%A9%E2%80%AD/@26.0698477,43.9820698,2863m/data=!3m1!1e3!4m6!3m5!1s0x15"/>
     <hyperlink ref="A66" r:id="rId61" display="فرع الرس" tooltip="https://www.google.com/maps?q=%D8%B9%D9%8A%D9%86+%D8%B3%D9%83%D9%88%D9%8A%D8%B1%D8%8C+QOUB8057%D8%8C+8057+%D8%B9%D8%A8%D8%AF%D8%A7%D9%84%D9%84%D9%87+%D8%A7%D9%84%D8%AF%D9%88%D8%B3%D9%8A%D8%8C+5235%D8%8C+%D8%AD%D9%8A+%D8%A7%D9%84%D9%85%D9%84%D9%83+%D9%81%D"/>
     <hyperlink ref="A67" r:id="rId62" display="فرع البدائع" tooltip="https://maps.app.goo.gl/52c9EyC3tvfQW3Hj9"/>
     <hyperlink ref="A68" r:id="rId63" display="فرع البكيرية" tooltip="https://maps.app.goo.gl/w4fsDxxXijjMj9iX7?g_st=com.google.maps.preview.copy"/>
-    <hyperlink ref="B64" r:id="rId64" display="https://maps.app.goo.gl/cq4C8CMqHKHPXpMQ9"/>
-    <hyperlink ref="B65" r:id="rId65" display="https://maps.app.goo.gl/bjFT5iksXKau4rfF9"/>
-    <hyperlink ref="B66" r:id="rId66" display="https://maps.app.goo.gl/hkxtS885QgTX4dJo9"/>
-    <hyperlink ref="B67" r:id="rId67" display="https://maps.app.goo.gl/gooWgHEZ53kUuA8V8"/>
-    <hyperlink ref="B68" r:id="rId68" display="https://maps.app.goo.gl/hQTyity1SUEZjsYY8"/>
+    <hyperlink ref="B64" r:id="rId64" display="https://maps.app.goo.gl/cq4C8CMqHKHPXpMQ9" tooltip="https://maps.app.goo.gl/cq4C8CMqHKHPXpMQ9"/>
+    <hyperlink ref="B65" r:id="rId65" display="https://maps.app.goo.gl/bjFT5iksXKau4rfF9" tooltip="https://maps.app.goo.gl/bjFT5iksXKau4rfF9"/>
+    <hyperlink ref="B66" r:id="rId66" display="https://maps.app.goo.gl/hkxtS885QgTX4dJo9" tooltip="https://maps.app.goo.gl/hkxtS885QgTX4dJo9"/>
+    <hyperlink ref="B67" r:id="rId67" display="https://maps.app.goo.gl/gooWgHEZ53kUuA8V8" tooltip="https://maps.app.goo.gl/gooWgHEZ53kUuA8V8"/>
+    <hyperlink ref="B68" r:id="rId68" display="https://maps.app.goo.gl/hQTyity1SUEZjsYY8" tooltip="https://maps.app.goo.gl/hQTyity1SUEZjsYY8"/>
     <hyperlink ref="A75" r:id="rId69" display="مختبرات وريد الطبية فرع وادي الدواسر" tooltip="https://maps.app.goo.gl/w71XDpAjt4bBLKYy5"/>
     <hyperlink ref="A76" r:id="rId70" display="فرع السليل" tooltip="https://maps.app.goo.gl/k5VuNGsxMW6sYNMz5"/>
-    <hyperlink ref="B75" r:id="rId71" display="https://maps.app.goo.gl/Xqs4TaBZFQJ5M6eTA"/>
-    <hyperlink ref="B76" r:id="rId72" display="https://maps.app.goo.gl/oEA35McujBKwLz3L8"/>
+    <hyperlink ref="B75" r:id="rId71" display="https://maps.app.goo.gl/Xqs4TaBZFQJ5M6eTA" tooltip="https://maps.app.goo.gl/Xqs4TaBZFQJ5M6eTA"/>
+    <hyperlink ref="B76" r:id="rId72" display="https://maps.app.goo.gl/oEA35McujBKwLz3L8" tooltip="https://maps.app.goo.gl/oEA35McujBKwLz3L8"/>
     <hyperlink ref="A80" r:id="rId73" display="فرع شقراء - شارع القارة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%B4%D9%82%D8%B1%D8%A7%D8%A1%E2%80%AD/@25.2295522,45.262146,840m/data=!3m2!1e3!4b1!4m6!3m5!1s0x"/>
     <hyperlink ref="A81" r:id="rId74" display="فرع شقراء - طريق الملك سعود" tooltip="https://maps.app.goo.gl/cv1cZA23qfz5kE9j6?g_st=ipc"/>
     <hyperlink ref="A82" r:id="rId75" display="فرع المجمعة" tooltip="https://www.google.com/maps?q=%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D9%85%D8%AC%D9%85%D8%B9%D8%A9,+Al+Mustaqbal,+Al+Majma'ah+15368,+Saudi+Arabia&amp;ftid=0x3e2a"/>
     <hyperlink ref="A84" r:id="rId76" display="فرع الزلفي - شارع موسى بن نصير" tooltip="https://g.co/kgs/XW6Db6s"/>
-    <hyperlink ref="B80" r:id="rId77" display="https://maps.app.goo.gl/zFA3AcbJTtvFwM2n8"/>
-    <hyperlink ref="B84" r:id="rId78" display="https://share.google/wV25WoYS4wMFFr020"/>
-    <hyperlink ref="B83" r:id="rId79" display="https://maps.app.goo.gl/Qycau3wCAVWRpnLb6"/>
-    <hyperlink ref="B82" r:id="rId80" display="https://maps.app.goo.gl/KEY5Hk5FoWi2V4n18"/>
-    <hyperlink ref="B81" r:id="rId81" display="https://maps.app.goo.gl/TU5z6t8GwCvFqkzX8"/>
+    <hyperlink ref="B80" r:id="rId77" display="https://maps.app.goo.gl/zFA3AcbJTtvFwM2n8" tooltip="https://maps.app.goo.gl/zFA3AcbJTtvFwM2n8"/>
+    <hyperlink ref="B84" r:id="rId78" display="https://share.google/wV25WoYS4wMFFr020" tooltip="https://share.google/wV25WoYS4wMFFr020"/>
+    <hyperlink ref="B83" r:id="rId79" display="https://maps.app.goo.gl/Qycau3wCAVWRpnLb6" tooltip="https://maps.app.goo.gl/Qycau3wCAVWRpnLb6"/>
+    <hyperlink ref="B82" r:id="rId80" display="https://maps.app.goo.gl/KEY5Hk5FoWi2V4n18" tooltip="https://maps.app.goo.gl/KEY5Hk5FoWi2V4n18"/>
+    <hyperlink ref="B81" r:id="rId81" display="https://maps.app.goo.gl/TU5z6t8GwCvFqkzX8" tooltip="https://maps.app.goo.gl/TU5z6t8GwCvFqkzX8"/>
     <hyperlink ref="B90" r:id="rId82" display="https://maps.app.goo.gl/QKNwn8YVHMwmg5UC8"/>
     <hyperlink ref="A98" r:id="rId83" display="فرع الدوادمي" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%AF%D9%88%D8%A7%D8%AF%D9%85%D9%8A%E2%80%AD/@24.545091,44.4442652,844m/data=!3m2!1e"/>
     <hyperlink ref="A99" r:id="rId84" display="فرع عفيف" tooltip="https://www.google.com/maps?q=%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%B9%D9%81%D9%8A%D9%81,+%D8%B7%D8%B1%D9%8A%D9%82+%D8%A7%D9%84%D9%85%D9%84%D9%83+%D8%B9%D8%A8%D8%AF%"/>
@@ -2661,16 +3301,92 @@
     <hyperlink ref="A107" r:id="rId88" display="فرع حوطة بني تميم" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%AD%D9%88%D8%B7%D8%A9+%D8%A8%D9%86%D9%8A+%D8%AA%D9%85%D9%8A%D9%85%E2%80%AD/@23.4911007,46.8817"/>
     <hyperlink ref="A108" r:id="rId89" display="فرع الخرج" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%AE%D8%B1%D8%AC%E2%80%AD/@24.1523125,47.2773125,17z/data=!3m1!4b1!4m6!3m5!1s0x3e25"/>
     <hyperlink ref="A109" r:id="rId90" display="فرع الافلاج" tooltip="https://maps.app.goo.gl/795YQUS6QeWypXk5A"/>
-    <hyperlink ref="B109" r:id="rId91" display="https://maps.app.goo.gl/YJPri1Ur1izBdWMw7"/>
-    <hyperlink ref="B108" r:id="rId92" display="https://maps.app.goo.gl/Q93ty5DM8EhVQWoh7"/>
-    <hyperlink ref="B107" r:id="rId93" display="https://maps.app.goo.gl/MCQEpB8CgUMaH31m8"/>
-    <hyperlink ref="B106" r:id="rId94" display="https://maps.app.goo.gl/AEHcEgix4ELgXT1z6"/>
-    <hyperlink ref="B105" r:id="rId95" display="https://maps.app.goo.gl/k8JNhKATqsngmRe78"/>
+    <hyperlink ref="B109" r:id="rId91" display="https://maps.app.goo.gl/YJPri1Ur1izBdWMw7" tooltip="https://maps.app.goo.gl/YJPri1Ur1izBdWMw7"/>
+    <hyperlink ref="B108" r:id="rId92" display="https://maps.app.goo.gl/Q93ty5DM8EhVQWoh7" tooltip="https://maps.app.goo.gl/Q93ty5DM8EhVQWoh7"/>
+    <hyperlink ref="B107" r:id="rId93" display="https://maps.app.goo.gl/MCQEpB8CgUMaH31m8" tooltip="https://maps.app.goo.gl/MCQEpB8CgUMaH31m8"/>
+    <hyperlink ref="B106" r:id="rId94" display="https://maps.app.goo.gl/AEHcEgix4ELgXT1z6" tooltip="https://maps.app.goo.gl/AEHcEgix4ELgXT1z6"/>
+    <hyperlink ref="B105" r:id="rId95" display="https://maps.app.goo.gl/k8JNhKATqsngmRe78" tooltip="https://maps.app.goo.gl/k8JNhKATqsngmRe78"/>
     <hyperlink ref="A114" r:id="rId96" display="فرع القويعية" tooltip="https://maps.app.goo.gl/fWN6XPYRjkTwMbTN7?g_st=com.google.maps.preview.copy"/>
     <hyperlink ref="A115" r:id="rId97" display="فرع المزاحمية" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D9%85%D8%B2%D8%A7%D8%AD%D9%85%D9%8A%D8%A9%E2%80%AD/@24.4720369,46.2723893,17z/data=!"/>
-    <hyperlink ref="B114" r:id="rId98" display="https://maps.app.goo.gl/yWpx66ajkeM4St6r8"/>
+    <hyperlink ref="B114" r:id="rId98" display="https://maps.app.goo.gl/yWpx66ajkeM4St6r8" tooltip="https://maps.app.goo.gl/yWpx66ajkeM4St6r8"/>
     <hyperlink ref="A119" r:id="rId99" display="فرع ثادق" tooltip="https://maps.app.goo.gl/dt8XhhuPD2skxms6A"/>
     <hyperlink ref="A120" r:id="rId100" display="فرع رماح" tooltip="https://maps.app.goo.gl/q33zBVeZ3ecgvryq8"/>
+    <hyperlink ref="D3" r:id="rId2" display="الفرع الرئيسي - النرجس ٢٤ ساعة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9%E2%80%AD/@24.8480376,46.6661876,15z/data=!4m6!3m5!1s0x3e2ee5cebd16ee93:0x3429acba7c6d8cab!8m2!3d24.8480376!4d46.6661"/>
+    <hyperlink ref="D4" r:id="rId3" display="فرع قرطبة ٢٤ ساعة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%82%D8%B1%D8%B7%D8%A8%D8%A9%E2%80%AD/@24.8074644,46.75643,843m/data=!3m2!1e3!4b1!4m6!3m5!1s0x3e2eff68df5e01ed:0xc"/>
+    <hyperlink ref="D5" r:id="rId4" display="فرع الروضة ٢٤ ساعة" tooltip="https://maps.app.goo.gl/kCmQRzg7hYZqdzYH6"/>
+    <hyperlink ref="D6" r:id="rId5" display="فرع الربوة ٢٤ ساعة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%B1%D8%A8%D9%88%D8%A9%E2%80%AD/@24.6979452,46.7714686,843m/data=!3m2!1e3!4b1!4m6!3"/>
+    <hyperlink ref="D7" r:id="rId6" display="فرع لبن ٢٤ ساعة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D9%84%D8%A8%D9%86%E2%80%AD/@24.6319133,46.565049,844m/data=!3m2!1e3!4b1!4m6!3m5!1s0x3e2f19e066b1"/>
+    <hyperlink ref="D8" r:id="rId7" display="فرع العريجاء ٢٤ ساعة" tooltip="https://maps.app.goo.gl/PSYQsgppZ5NY5XhP7"/>
+    <hyperlink ref="D9" r:id="rId8" display="فرع العليا ٢٤ ساعة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%B9%D9%84%D9%8A%D8%A7%E2%80%AD/@24.6935675,46.7017641,843m/data=!3m2!1e3!4b1!4m6!3"/>
+    <hyperlink ref="D10" r:id="rId9" display="فرع العزيزية ٢٤ ساعة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%B9%D8%B2%D9%8A%D8%B2%D9%8A%D8%A9%E2%80%AD/@24.5746744,46.7684915,844m/data=!3m2!1"/>
+    <hyperlink ref="D11" r:id="rId10" display="فرع طويق ٢٤ ساعة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%B7%D9%88%D9%8A%D9%82%E2%80%AD/@24.5844058,46.5831618,844m/data=!3m2!1e3!4b1!4m6!3m5!1s0x3e2f1"/>
+    <hyperlink ref="D12" r:id="rId11" display="فرع العارض ٢٤ ساعة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%B9%D8%A7%D8%B1%D8%B6%E2%80%AD/@24.8739597,46.6158201,211m/data=!3m1!1e3!4m6!3m5!1"/>
+    <hyperlink ref="D13" r:id="rId12" display="فرع النسيم ٢٤ ساعة" tooltip="https://www.google.com/maps?q=%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D8%A7%D9%84%D9%86%D8%B3%D9%8A%D9%85,+%D8%AD%D9%8A,+An+Nasim+Ash+Sharqi,+Riyadh+14241,+Saudi+Arabia&amp;ftid=0x3e2f019851450"/>
+    <hyperlink ref="D15" r:id="rId13" display="فرع التعاون ٢٤ ساعة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%AA%D8%B9%D8%A7%D9%88%D9%86%E2%80%AD/@24.7631382,46.700526,15.95z/data=!4m6!3m5!1s"/>
+    <hyperlink ref="D16" r:id="rId14" display="فرع السعادة" tooltip="https://maps.app.goo.gl/KxLym9az9nfhwNww8"/>
+    <hyperlink ref="D17" r:id="rId15" display="فرع الرمال" tooltip="https://maps.app.goo.gl/UWqe4Hvxd7wjPG6GA?g_st=com.google.maps.preview.copy"/>
+    <hyperlink ref="D18" r:id="rId16" display="فرع المهدية" tooltip="https://maps.app.goo.gl/LTJX5FLwwCupv8KE6?g_st=com.google.maps.preview.copy"/>
+    <hyperlink ref="D19" r:id="rId17" display="فرع الشفا" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%B4%D9%81%D8%A7%E2%80%AD/@24.5371712,46.6908278,844m/data=!3m2!1e3!4b1!4m6!3m5!1s0"/>
+    <hyperlink ref="D20" r:id="rId18" display="فرع البديعة" tooltip="https://www.google.com/maps?q=%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%A8%D8%AF%D9%8A%D8%B9%D8%A9,+Aishah+Bint+Abi+Bakr,+Shubra,+Riyadh+12988,+Saudi+Arabia&amp;"/>
+    <hyperlink ref="D21" r:id="rId19" display="فرع النظيم" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D9%86%D8%B8%D9%8A%D9%85%E2%80%AD/@24.8058533,46.8877865,17z/data=!3m1!4b1!4m6!3m5!1s"/>
+    <hyperlink ref="D22" r:id="rId20" display="فرع الدار البيضاء" tooltip="https://maps.app.goo.gl/VbJnyr8NTSYPu5JY6"/>
+    <hyperlink ref="D23" r:id="rId21" display="فرع العقيق" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%B9%D9%82%D9%8A%D9%82%E2%80%AD/@24.7815704,46.5735345,13.45z/data=!4m7!3m6!1s0x3e2"/>
+    <hyperlink ref="D24" r:id="rId22" display="فرع الحزم" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D8%A7%D9%84%D8%AD%D8%B2%D9%85%E2%80%AD/@24.5478014,46.6509543,17z/data=!3m1!4b1!4m6!3m5!1s0x3e2f11ef6ea2d3b7:0xe875"/>
+    <hyperlink ref="D25" r:id="rId23" display="فرع الدرعية" tooltip="https://maps.app.goo.gl/4P2Q5mfUQae3jFfH6"/>
+    <hyperlink ref="D30" r:id="rId34" display="فرع المحمدية تم الإفتتاح ٢٤ ساعة" tooltip="https://maps.app.goo.gl/c3hoJMdEFZuwm6HX7"/>
+    <hyperlink ref="D31" r:id="rId35" display="فرع الياقوت تم الإفتتاح" tooltip="https://maps.app.goo.gl/6EeBJpXvKMjKZZTf6"/>
+    <hyperlink ref="D32" r:id="rId36" display="فرع الحمدانية تم الإفتتاح" tooltip="https://maps.app.goo.gl/JPV4axnHsgxLXH4v6"/>
+    <hyperlink ref="D33" r:id="rId37" display="فرع السامر تم الإفتتاح" tooltip="https://maps.app.goo.gl/UyVnmvGkKLbKmGJz8"/>
+    <hyperlink ref="D34" r:id="rId38" display="فرع المروة تم الإفتتاح" tooltip="https://maps.app.goo.gl/DaCkbNzHF8yt2CrC9"/>
+    <hyperlink ref="D39" r:id="rId44" display="فرع العوالي - تم الافتتاح" tooltip="https://maps.app.goo.gl/Ab86Zf14wbbEeQjp6"/>
+    <hyperlink ref="D40" r:id="rId45" display="فرع الشوقية - تم الافتتاح" tooltip="https://maps.app.goo.gl/2ndi9JxFBkWbaZqU7"/>
+    <hyperlink ref="D41" r:id="rId46" display="فرع الشرايع - قريبا الافتتاح" tooltip="https://maps.app.goo.gl/GykJXxYSLrA9xqh89"/>
+    <hyperlink ref="D45" r:id="rId50" display="فرع الطائف شارع شهار" tooltip="https://maps.app.goo.gl/tnQpq8q3UA7PWLRQ9"/>
+    <hyperlink ref="D46" r:id="rId51" display="فرع الطائف - شارع السحيلي" tooltip="https://maps.app.goo.gl/N8gmy9MrJfFdrfoFA"/>
+    <hyperlink ref="D58" r:id="rId55" display="موقع فرع حائل - طريق الملك سعود" tooltip="https://maps.app.goo.gl/xkZkMr7NSddrjaJW6"/>
+    <hyperlink ref="D59" r:id="rId56" display="موقع فرع حائل الثاني - طريق جدة تم الإفتتاح" tooltip="https://maps.app.goo.gl/T51u2WDJKX2BviDr5"/>
+    <hyperlink ref="D64" r:id="rId59" display="فرع بريدة ٢٤ ساعة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A8%D8%B1%D9%8A%D8%AF%D9%87%E2%80%AD/@26.4042432,43.9140287,1261m/data=!3m2!1e3!4b1!4m6!3m5!1s"/>
+    <hyperlink ref="D65" r:id="rId60" display="فرع عنيزة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%B9%D9%86%D9%8A%D8%B2%D8%A9%E2%80%AD/@26.0698477,43.9820698,2863m/data=!3m1!1e3!4m6!3m5!1s0x15"/>
+    <hyperlink ref="D66" r:id="rId61" display="فرع الرس" tooltip="https://www.google.com/maps?q=%D8%B9%D9%8A%D9%86+%D8%B3%D9%83%D9%88%D9%8A%D8%B1%D8%8C+QOUB8057%D8%8C+8057+%D8%B9%D8%A8%D8%AF%D8%A7%D9%84%D9%84%D9%87+%D8%A7%D9%84%D8%AF%D9%88%D8%B3%D9%8A%D8%8C+5235%D8%8C+%D8%AD%D9%8A+%D8%A7%D9%84%D9%85%D9%84%D9%83+%D9%81%D"/>
+    <hyperlink ref="D67" r:id="rId62" display="فرع البدائع" tooltip="https://maps.app.goo.gl/52c9EyC3tvfQW3Hj9"/>
+    <hyperlink ref="D68" r:id="rId63" display="فرع البكيرية" tooltip="https://maps.app.goo.gl/w4fsDxxXijjMj9iX7?g_st=com.google.maps.preview.copy"/>
+    <hyperlink ref="D75" r:id="rId69" display="مختبرات وريد الطبية فرع وادي الدواسر" tooltip="https://maps.app.goo.gl/w71XDpAjt4bBLKYy5"/>
+    <hyperlink ref="D76" r:id="rId70" display="فرع السليل" tooltip="https://maps.app.goo.gl/k5VuNGsxMW6sYNMz5"/>
+    <hyperlink ref="D80" r:id="rId73" display="فرع شقراء - شارع القارة" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%B4%D9%82%D8%B1%D8%A7%D8%A1%E2%80%AD/@25.2295522,45.262146,840m/data=!3m2!1e3!4b1!4m6!3m5!1s0x"/>
+    <hyperlink ref="D81" r:id="rId74" display="فرع شقراء - طريق الملك سعود" tooltip="https://maps.app.goo.gl/cv1cZA23qfz5kE9j6?g_st=ipc"/>
+    <hyperlink ref="D82" r:id="rId75" display="فرع المجمعة" tooltip="https://www.google.com/maps?q=%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D9%85%D8%AC%D9%85%D8%B9%D8%A9,+Al+Mustaqbal,+Al+Majma'ah+15368,+Saudi+Arabia&amp;ftid=0x3e2a"/>
+    <hyperlink ref="D84" r:id="rId76" display="فرع الزلفي - شارع موسى بن نصير" tooltip="https://g.co/kgs/XW6Db6s"/>
+    <hyperlink ref="D98" r:id="rId83" display="فرع الدوادمي" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%AF%D9%88%D8%A7%D8%AF%D9%85%D9%8A%E2%80%AD/@24.545091,44.4442652,844m/data=!3m2!1e"/>
+    <hyperlink ref="D99" r:id="rId84" display="فرع عفيف" tooltip="https://www.google.com/maps?q=%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%B9%D9%81%D9%8A%D9%81,+%D8%B7%D8%B1%D9%8A%D9%82+%D8%A7%D9%84%D9%85%D9%84%D9%83+%D8%B9%D8%A8%D8%AF%"/>
+    <hyperlink ref="D100" r:id="rId85" display="فرع ساجر" tooltip="https://www.google.com/maps?q=25.1878326,44.6011418&amp;entry=gps&amp;lucs=,94246480,94242508,94224825,94227247,94227248,47071704,47069508,94218641,94228354,94233079,94203019,47084304,94208458,94208447,94213318&amp;g_ep=CAISEjI0LjQ3LjMuNjk4NTMxOTU1MBgAIKzfASqHASw5NDI"/>
+    <hyperlink ref="D105" r:id="rId86" display="فرع الخرج ( الزاهر )" tooltip="https://maps.app.goo.gl/PzzPZuNX2to54xTh6?g_st=com.google.maps.preview.copy"/>
+    <hyperlink ref="D106" r:id="rId87" display="فرع الدلم" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%AF%D9%84%D9%85%E2%80%AD/@23.9956215,47.1345243,17z/data=!3m1!4b1!4m6!3m5!1s0x3e25"/>
+    <hyperlink ref="D107" r:id="rId88" display="فرع حوطة بني تميم" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%AD%D9%88%D8%B7%D8%A9+%D8%A8%D9%86%D9%8A+%D8%AA%D9%85%D9%8A%D9%85%E2%80%AD/@23.4911007,46.8817"/>
+    <hyperlink ref="D108" r:id="rId89" display="فرع الخرج" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D8%AE%D8%B1%D8%AC%E2%80%AD/@24.1523125,47.2773125,17z/data=!3m1!4b1!4m6!3m5!1s0x3e25"/>
+    <hyperlink ref="D109" r:id="rId90" display="فرع الافلاج" tooltip="https://maps.app.goo.gl/795YQUS6QeWypXk5A"/>
+    <hyperlink ref="D114" r:id="rId96" display="فرع القويعية" tooltip="https://maps.app.goo.gl/fWN6XPYRjkTwMbTN7?g_st=com.google.maps.preview.copy"/>
+    <hyperlink ref="D115" r:id="rId97" display="فرع المزاحمية" tooltip="https://www.google.com/maps/place/%D9%85%D8%AE%D8%AA%D8%A8%D8%B1%D8%A7%D8%AA+%D9%88%D8%B1%D9%8A%D8%AF+%D8%A7%D9%84%D8%B7%D8%A8%D9%8A%D8%A9+%D9%81%D8%B1%D8%B9+%D8%A7%D9%84%D9%85%D8%B2%D8%A7%D8%AD%D9%85%D9%8A%D8%A9%E2%80%AD/@24.4720369,46.2723893,17z/data=!"/>
+    <hyperlink ref="D119" r:id="rId99" display="فرع ثادق" tooltip="https://maps.app.goo.gl/dt8XhhuPD2skxms6A"/>
+    <hyperlink ref="D120" r:id="rId100" display="فرع رماح" tooltip="https://maps.app.goo.gl/q33zBVeZ3ecgvryq8"/>
+    <hyperlink ref="B98" r:id="rId101" display="https://maps.app.goo.gl/dUFRrz8f2eeXCiNn6"/>
+    <hyperlink ref="B99" r:id="rId102" display="https://maps.app.goo.gl/nzvyZHUNDoNaHets9"/>
+    <hyperlink ref="B100" r:id="rId103" display="https://maps.app.goo.gl/6D48sqHtkLi4mp1h9"/>
+    <hyperlink ref="B115" r:id="rId104" display="https://maps.app.goo.gl/KkEw24dLoDJWejew5"/>
+    <hyperlink ref="B119" r:id="rId105" display="https://maps.app.goo.gl/jUTwzGVzr5BoDPoPA"/>
+    <hyperlink ref="B120" r:id="rId106" display="https://maps.app.goo.gl/ExRx5qL1a7KvajjD6"/>
+    <hyperlink ref="B3" r:id="rId107" display="https://maps.app.goo.gl/7RKTqwjUksjCMvsN6"/>
+    <hyperlink ref="B5" r:id="rId108" display="https://maps.app.goo.gl/FXyn23sBjoCC3boi8"/>
+    <hyperlink ref="B6" r:id="rId109" display="https://maps.app.goo.gl/HorzLnBWrWj2vz9p7"/>
+    <hyperlink ref="B7" r:id="rId110" display="https://maps.app.goo.gl/BJiPNb2PUho7t7RA8"/>
+    <hyperlink ref="B9" r:id="rId111" display="https://maps.app.goo.gl/D9s3JQDa5tTQgV279"/>
+    <hyperlink ref="B10" r:id="rId112" display="https://maps.app.goo.gl/YEFuPyUHAdZA9HVH7"/>
+    <hyperlink ref="B13" r:id="rId113" display="https://maps.app.goo.gl/n2UTYG5mH2dfx8BcA"/>
+    <hyperlink ref="B14" r:id="rId114" display="https://maps.app.goo.gl/xF6boZ9RELk8NPKM9"/>
+    <hyperlink ref="B15" r:id="rId115" display="https://maps.app.goo.gl/NBiLwh6ktW9WA9Mq5"/>
+    <hyperlink ref="B16" r:id="rId116" display="https://maps.app.goo.gl/MCYibuYz3Zytyc7X6"/>
+    <hyperlink ref="B17" r:id="rId117" display="https://maps.app.goo.gl/RwaHDGJ3YCwdXvFy7"/>
+    <hyperlink ref="B19" r:id="rId118" display="https://maps.app.goo.gl/JDzuwJfHcQ9y2Qzx9"/>
+    <hyperlink ref="B22" r:id="rId119" display="https://maps.app.goo.gl/cNatQTdSQPrpTPCD7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
